--- a/artfynd/A 11826-2026 artfynd.xlsx
+++ b/artfynd/A 11826-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91184653</v>
       </c>
       <c r="B2" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767113.2359142913</v>
+        <v>767113</v>
       </c>
       <c r="R2" t="n">
-        <v>7084697.593520858</v>
+        <v>7084698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-02-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99284837</v>
+        <v>130297493</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxviken O Tavlefjärden, Innertavle, Vb</t>
+          <t>Oxviken, Innertavle, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767111.2069221559</v>
+        <v>767107</v>
       </c>
       <c r="R3" t="n">
-        <v>7084700.52953669</v>
+        <v>7084707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +866,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>död gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,7 +877,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,12 +887,7 @@
         <v>107621763</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767105.2795199542</v>
+        <v>767105</v>
       </c>
       <c r="R4" t="n">
-        <v>7084702.245158169</v>
+        <v>7084702</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -991,19 +961,9 @@
           <t>2023-03-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297493</v>
+        <v>125328555</v>
       </c>
       <c r="B5" t="n">
-        <v>4773</v>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,14 +1026,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxviken, Innertavle, Vb</t>
+          <t>Sillviksvägen O Oxviken, Innertavle, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767107</v>
+        <v>767138</v>
       </c>
       <c r="R5" t="n">
-        <v>7084707</v>
+        <v>7084654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11826-2026 artfynd.xlsx
+++ b/artfynd/A 11826-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91184653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130297493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107621763</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,8 +1114,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125328555</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>